--- a/docentes/Santiago Hernández Mariana - Estadisticos 20232.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -67,31 +67,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ROBLES</t>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
   </si>
   <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>NAVARRO</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
+  </si>
+  <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
   </si>
   <si>
     <t>JORGE MARIO</t>
   </si>
   <si>
-    <t>JORGE GUILLERMO</t>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>DARINKA</t>
   </si>
 </sst>
 </file>
@@ -557,16 +584,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>57.14</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -622,16 +652,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>64.29000000000001</v>
+        <v>57.14</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -641,7 +671,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -673,16 +703,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920207</v>
+        <v>21330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -696,16 +726,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920209</v>
+        <v>21330051920386</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -719,16 +749,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920190</v>
+        <v>21330051920209</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -737,6 +767,75 @@
         <v>9</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920199</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920212</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920214</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20232.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -67,58 +67,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>DARINKA</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
   </si>
 </sst>
 </file>
@@ -652,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>57.14</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H2">
         <v>6.7</v>
@@ -671,7 +662,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -703,16 +694,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920190</v>
+        <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -726,16 +717,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920386</v>
+        <v>21330051920202</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -749,16 +740,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920209</v>
+        <v>21330051920203</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -772,16 +763,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920199</v>
+        <v>21330051920213</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -790,21 +781,21 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920212</v>
+        <v>21330051920201</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -813,29 +804,6 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920214</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>
